--- a/data/compendium_schema (Joe).xlsx
+++ b/data/compendium_schema (Joe).xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27928"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ennsj\Documents\3. Management Domains\Interactive Tool\R Code\salmon_management_domains_compendium\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ennsj\Documents\3. Management Domains\Interactive Tool\R Code\salmon_management_domains_compendium\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9950DE5F-8CB0-4AA2-9DE5-FABA9011D053}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{391BC435-8ED0-4EA0-A5C8-147934ACFE89}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="1485" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{C8DE9B6A-1A32-438B-AB2C-1ED60489CD7B}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{C8DE9B6A-1A32-438B-AB2C-1ED60489CD7B}"/>
   </bookViews>
   <sheets>
     <sheet name="Schema" sheetId="1" r:id="rId1"/>
@@ -51,7 +51,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="47">
   <si>
     <t>Section</t>
   </si>
@@ -165,33 +165,6 @@
   </si>
   <si>
     <t>ranking_id</t>
-  </si>
-  <si>
-    <t>NOAA_ecological_concern</t>
-  </si>
-  <si>
-    <t>RAMS_LF_category</t>
-  </si>
-  <si>
-    <t>RAMS_LF</t>
-  </si>
-  <si>
-    <t>ID</t>
-  </si>
-  <si>
-    <t>definition</t>
-  </si>
-  <si>
-    <t>included_categories</t>
-  </si>
-  <si>
-    <t>sub_ID</t>
-  </si>
-  <si>
-    <t>ecological_concern_sub_category</t>
-  </si>
-  <si>
-    <t>Primary Lifestages Affected</t>
   </si>
   <si>
     <t>agencies</t>
@@ -640,16 +613,6 @@
 </file>
 
 <file path=xl/tables/table10.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{EB7250C4-9765-42FA-BDCB-69E1EDA90C21}" name="Table8" displayName="Table8" ref="O1:O11" totalsRowShown="0">
-  <autoFilter ref="O1:O11" xr:uid="{EB7250C4-9765-42FA-BDCB-69E1EDA90C21}"/>
-  <tableColumns count="1">
-    <tableColumn id="1" xr3:uid="{2576247A-3067-4CAE-B18B-E28518257AB5}" name="NOAA_ecological_concern"/>
-  </tableColumns>
-  <tableStyleInfo name="TableStyleMedium3" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
-</table>
-</file>
-
-<file path=xl/tables/table11.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{9C4DBBFE-4A86-48E2-B101-152A6BF9BE52}" name="Table9" displayName="Table9" ref="C1:C4" totalsRowShown="0">
   <autoFilter ref="C1:C4" xr:uid="{9C4DBBFE-4A86-48E2-B101-152A6BF9BE52}"/>
   <tableColumns count="1">
@@ -740,9 +703,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -780,7 +743,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -886,7 +849,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1028,7 +991,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1036,38 +999,37 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D9B93BC3-A7C7-4C7C-B60E-FF9A84A5B5E6}">
-  <dimension ref="A1:O21"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:M21"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="23.453125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="3.453125" customWidth="1"/>
-    <col min="3" max="3" width="10.6328125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="2.90625" customWidth="1"/>
-    <col min="5" max="5" width="29.81640625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="3.36328125" customWidth="1"/>
-    <col min="7" max="7" width="20.36328125" customWidth="1"/>
-    <col min="8" max="8" width="4.08984375" customWidth="1"/>
-    <col min="9" max="9" width="24.81640625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="5.26953125" customWidth="1"/>
-    <col min="11" max="11" width="33.90625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="3.54296875" customWidth="1"/>
-    <col min="13" max="13" width="23.453125" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="3.6328125" customWidth="1"/>
-    <col min="15" max="15" width="29.81640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="23.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="3.42578125" customWidth="1"/>
+    <col min="3" max="3" width="10.5703125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="2.85546875" customWidth="1"/>
+    <col min="5" max="5" width="29.85546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="3.42578125" customWidth="1"/>
+    <col min="7" max="7" width="20.42578125" customWidth="1"/>
+    <col min="8" max="8" width="4.140625" customWidth="1"/>
+    <col min="9" max="9" width="24.85546875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="5.28515625" customWidth="1"/>
+    <col min="11" max="11" width="33.85546875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="3.5703125" customWidth="1"/>
+    <col min="13" max="13" width="23.42578125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="3.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C1" t="s">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>50</v>
+        <v>41</v>
       </c>
       <c r="G1" t="s">
-        <v>51</v>
+        <v>42</v>
       </c>
       <c r="I1" t="s">
         <v>16</v>
@@ -1078,11 +1040,8 @@
       <c r="M1" t="s">
         <v>22</v>
       </c>
-      <c r="O1" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2" s="10" t="s">
         <v>3</v>
       </c>
@@ -1105,16 +1064,13 @@
       <c r="M2" t="s">
         <v>23</v>
       </c>
-      <c r="O2" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
         <v>4</v>
       </c>
       <c r="C3" t="s">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="E3" s="10" t="s">
         <v>21</v>
@@ -1132,22 +1088,19 @@
       <c r="M3" t="s">
         <v>24</v>
       </c>
-      <c r="O3" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="s">
         <v>5</v>
       </c>
       <c r="C4" t="s">
-        <v>49</v>
+        <v>40</v>
       </c>
       <c r="E4" s="5" t="s">
         <v>0</v>
       </c>
       <c r="G4" s="5" t="s">
-        <v>54</v>
+        <v>45</v>
       </c>
       <c r="J4" s="5"/>
       <c r="K4" s="9" t="s">
@@ -1156,11 +1109,8 @@
       <c r="M4" t="s">
         <v>25</v>
       </c>
-      <c r="O4" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A5" s="8" t="s">
         <v>6</v>
       </c>
@@ -1180,11 +1130,8 @@
       <c r="M5" t="s">
         <v>26</v>
       </c>
-      <c r="O5" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
         <v>7</v>
       </c>
@@ -1200,11 +1147,8 @@
       <c r="M6" t="s">
         <v>27</v>
       </c>
-      <c r="O6" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
       <c r="G7" s="5" t="s">
         <v>8</v>
       </c>
@@ -1214,22 +1158,16 @@
       <c r="M7" t="s">
         <v>28</v>
       </c>
-      <c r="O7" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
       <c r="G8" s="4"/>
       <c r="J8" s="5"/>
       <c r="K8" s="5"/>
       <c r="M8" t="s">
         <v>29</v>
       </c>
-      <c r="O8" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
       <c r="E9" s="2"/>
       <c r="H9" s="3"/>
       <c r="I9" t="s">
@@ -1240,11 +1178,8 @@
       <c r="M9" t="s">
         <v>30</v>
       </c>
-      <c r="O9" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
       <c r="G10" s="3"/>
       <c r="H10" s="3"/>
       <c r="I10" s="5" t="s">
@@ -1253,11 +1188,8 @@
       <c r="M10" t="s">
         <v>31</v>
       </c>
-      <c r="O10" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
       <c r="G11" s="3"/>
       <c r="I11" s="12" t="s">
         <v>17</v>
@@ -1265,11 +1197,8 @@
       <c r="M11" t="s">
         <v>32</v>
       </c>
-      <c r="O11" s="6" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
       <c r="G12" s="3"/>
       <c r="J12" s="5"/>
       <c r="K12" s="5"/>
@@ -1277,9 +1206,9 @@
         <v>33</v>
       </c>
     </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
       <c r="I13" t="s">
-        <v>52</v>
+        <v>43</v>
       </c>
       <c r="J13" s="5"/>
       <c r="K13" s="5"/>
@@ -1287,7 +1216,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
       <c r="I14" s="16" t="s">
         <v>11</v>
       </c>
@@ -1295,7 +1224,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
       <c r="I15" s="13" t="s">
         <v>10</v>
       </c>
@@ -1303,7 +1232,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
       <c r="I16" s="14" t="s">
         <v>17</v>
       </c>
@@ -1313,12 +1242,12 @@
         <v>36</v>
       </c>
     </row>
-    <row r="17" spans="10:13" x14ac:dyDescent="0.35">
+    <row r="17" spans="10:13" x14ac:dyDescent="0.25">
       <c r="M17" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="21" spans="10:13" x14ac:dyDescent="0.35">
+    <row r="21" spans="10:13" x14ac:dyDescent="0.25">
       <c r="J21" s="5"/>
       <c r="K21" s="5"/>
     </row>
@@ -1328,7 +1257,7 @@
   <headerFooter>
     <oddHeader>&amp;R&amp;"Calibri"&amp;12&amp;K000000 Unclassified - Non-Classifié&amp;1#_x000D_</oddHeader>
   </headerFooter>
-  <tableParts count="11">
+  <tableParts count="10">
     <tablePart r:id="rId1"/>
     <tablePart r:id="rId2"/>
     <tablePart r:id="rId3"/>
@@ -1339,7 +1268,6 @@
     <tablePart r:id="rId8"/>
     <tablePart r:id="rId9"/>
     <tablePart r:id="rId10"/>
-    <tablePart r:id="rId11"/>
   </tableParts>
 </worksheet>
 </file>
@@ -1347,31 +1275,31 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{73336E6D-58B7-470B-B63A-57C23AF01533}">
   <dimension ref="A1:A6"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="88.1796875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="88.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" ht="159.5" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:1" ht="180" x14ac:dyDescent="0.25">
       <c r="A1" s="17" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.35">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="17"/>
     </row>
-    <row r="3" spans="1:1" ht="391.5" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:1" ht="405" x14ac:dyDescent="0.25">
       <c r="A3" s="17" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.35">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" s="17"/>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" s="17"/>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" s="17"/>
     </row>
   </sheetData>
